--- a/data/daschland_ontology/daschland (Alice in DaSCHland)/resources.xlsx
+++ b/data/daschland_ontology/daschland (Alice in DaSCHland)/resources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/0854-daschland-scripts/data/daschland_ontology/daschland (Alice in DaSCHland)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/Customer_Projects/daschland-scripts/data/daschland_ontology/daschland (Alice in DaSCHland)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DE1652-E516-8144-8B70-E77AE8C31701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4ACE1F-4646-5D42-B27F-C30BF34AF130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" tabRatio="500" firstSheet="4" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" tabRatio="500" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSc
@@ -80,7 +80,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwRg
@@ -97,7 +97,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTA
@@ -114,7 +114,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSo
@@ -143,7 +143,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -160,7 +160,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -191,7 +191,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTI
@@ -208,7 +208,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwT0
@@ -229,7 +229,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwR8
@@ -257,7 +257,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -274,7 +274,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -305,7 +305,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -322,7 +322,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -353,7 +353,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSw
@@ -370,7 +370,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwRc
@@ -391,7 +391,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSU
@@ -419,7 +419,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwR4
@@ -436,7 +436,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwS0
@@ -457,7 +457,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTo
@@ -485,7 +485,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTY
@@ -502,7 +502,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSQ
@@ -523,7 +523,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSA
@@ -551,7 +551,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTY
@@ -568,7 +568,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSQ
@@ -589,7 +589,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSA
@@ -617,7 +617,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTY
@@ -634,7 +634,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSQ
@@ -655,7 +655,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwSA
@@ -683,7 +683,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -700,7 +700,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -731,7 +731,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -748,7 +748,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -779,7 +779,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -796,7 +796,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -827,7 +827,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -844,7 +844,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -875,7 +875,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTM
@@ -892,7 +892,7 @@
             <sz val="12"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>======
 ID#AAAA48CmwTk
@@ -911,7 +911,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="224">
   <si>
     <t>name</t>
   </si>
@@ -1580,6 +1580,9 @@
   </si>
   <si>
     <t>hasCast</t>
+  </si>
+  <si>
+    <t>hasPreview</t>
   </si>
 </sst>
 </file>
@@ -3789,7 +3792,15 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="9"/>
+      <c r="A6" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="9"/>
@@ -6793,7 +6804,7 @@
         <v>186</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -6804,7 +6815,7 @@
         <v>186</v>
       </c>
       <c r="C3" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/daschland_ontology/daschland (Alice in DaSCHland)/resources.xlsx
+++ b/data/daschland_ontology/daschland (Alice in DaSCHland)/resources.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/Customer_Projects/daschland-scripts/data/daschland_ontology/daschland (Alice in DaSCHland)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4ACE1F-4646-5D42-B27F-C30BF34AF130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355C1AC9-978C-0949-911D-ABC14FB599AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20460" tabRatio="500" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -911,7 +911,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="225">
   <si>
     <t>name</t>
   </si>
@@ -1583,6 +1583,9 @@
   </si>
   <si>
     <t>hasPreview</t>
+  </si>
+  <si>
+    <t>hasGeolocation</t>
   </si>
 </sst>
 </file>
@@ -6779,7 +6782,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
@@ -6808,14 +6811,25 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>192</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="6">
-        <v>7</v>
+      <c r="C4" s="6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
